--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrExchangeImport.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrExchangeImport.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView windowWidth="19815" windowHeight="7860"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
@@ -17,79 +17,63 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>序号</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>组合代码</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>资金账户</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>资金账号代码</t>
   </si>
   <si>
-    <t>证券代码</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>资产代码</t>
   </si>
   <si>
     <t>委托方向</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>价格模式</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>指令价格</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>全价价格</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>收益率(%)</t>
   </si>
   <si>
     <t>指令数量</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>指令金额</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>开始日期</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>结束日期</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>收益率(%)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="0.000_ "/>
-    <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="8">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="0.000_ "/>
     <numFmt numFmtId="178" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="179" formatCode="#,##0.00_);[Red]\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -98,22 +82,14 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -121,20 +97,356 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -142,62 +454,348 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="26" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -246,7 +844,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -281,7 +879,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -484,14 +1082,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
   <cols>
     <col min="2" max="2" width="15.5" customWidth="1"/>
     <col min="3" max="3" width="12.375" customWidth="1"/>
@@ -501,7 +1099,7 @@
     <col min="13" max="13" width="12.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" s="1" customFormat="1" spans="1:13">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -526,126 +1124,126 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="J1" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="8" t="s">
-        <v>11</v>
-      </c>
     </row>
-    <row r="2" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="9"/>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
+    <row r="2" s="2" customFormat="1" spans="1:13">
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
     </row>
-    <row r="3" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
+    <row r="3" s="2" customFormat="1" spans="1:13">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
     </row>
-    <row r="4" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
+    <row r="4" s="2" customFormat="1" spans="1:13">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
     </row>
-    <row r="5" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="14"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
+    <row r="5" s="2" customFormat="1" spans="1:13">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="14"/>
     </row>
-    <row r="6" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
+    <row r="6" s="2" customFormat="1" spans="1:13">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="14"/>
     </row>
-    <row r="7" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="14"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
+    <row r="7" s="2" customFormat="1" spans="1:13">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="13"/>
+      <c r="L7" s="14"/>
+      <c r="M7" s="14"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="WVM6 JA6 SW6 ACS6 AMO6 AWK6 BGG6 BQC6 BZY6 CJU6 CTQ6 DDM6 DNI6 DXE6 EHA6 EQW6 FAS6 FKO6 FUK6 GEG6 GOC6 GXY6 HHU6 HRQ6 IBM6 ILI6 IVE6 JFA6 JOW6 JYS6 KIO6 KSK6 LCG6 LMC6 LVY6 MFU6 MPQ6 MZM6 NJI6 NTE6 ODA6 OMW6 OWS6 PGO6 PQK6 QAG6 QKC6 QTY6 RDU6 RNQ6 RXM6 SHI6 SRE6 TBA6 TKW6 TUS6 UEO6 UOK6 UYG6 VIC6 VRY6 WBU6 WLQ6 E1:E1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="JA6 SW6 ACS6 AMO6 AWK6 BGG6 BQC6 BZY6 CJU6 CTQ6 DDM6 DNI6 DXE6 EHA6 EQW6 FAS6 FKO6 FUK6 GEG6 GOC6 GXY6 HHU6 HRQ6 IBM6 ILI6 IVE6 JFA6 JOW6 JYS6 KIO6 KSK6 LCG6 LMC6 LVY6 MFU6 MPQ6 MZM6 NJI6 NTE6 ODA6 OMW6 OWS6 PGO6 PQK6 QAG6 QKC6 QTY6 RDU6 RNQ6 RXM6 SHI6 SRE6 TBA6 TKW6 TUS6 UEO6 UOK6 UYG6 VIC6 VRY6 WBU6 WLQ6 WVM6 E$1:E$1048576">
       <formula1>"买入,卖出,申购,配股,配债,行权-回售,债转股,质押券入库,质押券出库,正回购,逆回购"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="WVM7 JA1:JA5 SW1:SW5 ACS1:ACS5 AMO1:AMO5 AWK1:AWK5 BGG1:BGG5 BQC1:BQC5 BZY1:BZY5 CJU1:CJU5 CTQ1:CTQ5 DDM1:DDM5 DNI1:DNI5 DXE1:DXE5 EHA1:EHA5 EQW1:EQW5 FAS1:FAS5 FKO1:FKO5 FUK1:FUK5 GEG1:GEG5 GOC1:GOC5 GXY1:GXY5 HHU1:HHU5 HRQ1:HRQ5 IBM1:IBM5 ILI1:ILI5 IVE1:IVE5 JFA1:JFA5 JOW1:JOW5 JYS1:JYS5 KIO1:KIO5 KSK1:KSK5 LCG1:LCG5 LMC1:LMC5 LVY1:LVY5 MFU1:MFU5 MPQ1:MPQ5 MZM1:MZM5 NJI1:NJI5 NTE1:NTE5 ODA1:ODA5 OMW1:OMW5 OWS1:OWS5 PGO1:PGO5 PQK1:PQK5 QAG1:QAG5 QKC1:QKC5 QTY1:QTY5 RDU1:RDU5 RNQ1:RNQ5 RXM1:RXM5 SHI1:SHI5 SRE1:SRE5 TBA1:TBA5 TKW1:TKW5 TUS1:TUS5 UEO1:UEO5 UOK1:UOK5 UYG1:UYG5 VIC1:VIC5 VRY1:VRY5 WBU1:WBU5 WLQ1:WLQ5 WVM1:WVM5 WLQ7 JA7 SW7 ACS7 AMO7 AWK7 BGG7 BQC7 BZY7 CJU7 CTQ7 DDM7 DNI7 DXE7 EHA7 EQW7 FAS7 FKO7 FUK7 GEG7 GOC7 GXY7 HHU7 HRQ7 IBM7 ILI7 IVE7 JFA7 JOW7 JYS7 KIO7 KSK7 LCG7 LMC7 LVY7 MFU7 MPQ7 MZM7 NJI7 NTE7 ODA7 OMW7 OWS7 PGO7 PQK7 QAG7 QKC7 QTY7 RDU7 RNQ7 RXM7 SHI7 SRE7 TBA7 TKW7 TUS7 UEO7 UOK7 UYG7 VIC7 VRY7 WBU7">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="JA7 SW7 ACS7 AMO7 AWK7 BGG7 BQC7 BZY7 CJU7 CTQ7 DDM7 DNI7 DXE7 EHA7 EQW7 FAS7 FKO7 FUK7 GEG7 GOC7 GXY7 HHU7 HRQ7 IBM7 ILI7 IVE7 JFA7 JOW7 JYS7 KIO7 KSK7 LCG7 LMC7 LVY7 MFU7 MPQ7 MZM7 NJI7 NTE7 ODA7 OMW7 OWS7 PGO7 PQK7 QAG7 QKC7 QTY7 RDU7 RNQ7 RXM7 SHI7 SRE7 TBA7 TKW7 TUS7 UEO7 UOK7 UYG7 VIC7 VRY7 WBU7 WLQ7 WVM7 JA1:JA5 SW1:SW5 ACS1:ACS5 AMO1:AMO5 AWK1:AWK5 BGG1:BGG5 BQC1:BQC5 BZY1:BZY5 CJU1:CJU5 CTQ1:CTQ5 DDM1:DDM5 DNI1:DNI5 DXE1:DXE5 EHA1:EHA5 EQW1:EQW5 FAS1:FAS5 FKO1:FKO5 FUK1:FUK5 GEG1:GEG5 GOC1:GOC5 GXY1:GXY5 HHU1:HHU5 HRQ1:HRQ5 IBM1:IBM5 ILI1:ILI5 IVE1:IVE5 JFA1:JFA5 JOW1:JOW5 JYS1:JYS5 KIO1:KIO5 KSK1:KSK5 LCG1:LCG5 LMC1:LMC5 LVY1:LVY5 MFU1:MFU5 MPQ1:MPQ5 MZM1:MZM5 NJI1:NJI5 NTE1:NTE5 ODA1:ODA5 OMW1:OMW5 OWS1:OWS5 PGO1:PGO5 PQK1:PQK5 QAG1:QAG5 QKC1:QKC5 QTY1:QTY5 RDU1:RDU5 RNQ1:RNQ5 RXM1:RXM5 SHI1:SHI5 SRE1:SRE5 TBA1:TBA5 TKW1:TKW5 TUS1:TUS5 UEO1:UEO5 UOK1:UOK5 UYG1:UYG5 VIC1:VIC5 VRY1:VRY5 WBU1:WBU5 WLQ1:WLQ5 WVM1:WVM5">
       <formula1>"买入,卖出,申购,配股,配债,行权-回售,债转股,质押入库,质押出库,正回购,逆回购"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="WVN1:WVN7 JB1:JB7 SX1:SX7 ACT1:ACT7 AMP1:AMP7 AWL1:AWL7 BGH1:BGH7 BQD1:BQD7 BZZ1:BZZ7 CJV1:CJV7 CTR1:CTR7 DDN1:DDN7 DNJ1:DNJ7 DXF1:DXF7 EHB1:EHB7 EQX1:EQX7 FAT1:FAT7 FKP1:FKP7 FUL1:FUL7 GEH1:GEH7 GOD1:GOD7 GXZ1:GXZ7 HHV1:HHV7 HRR1:HRR7 IBN1:IBN7 ILJ1:ILJ7 IVF1:IVF7 JFB1:JFB7 JOX1:JOX7 JYT1:JYT7 KIP1:KIP7 KSL1:KSL7 LCH1:LCH7 LMD1:LMD7 LVZ1:LVZ7 MFV1:MFV7 MPR1:MPR7 MZN1:MZN7 NJJ1:NJJ7 NTF1:NTF7 ODB1:ODB7 OMX1:OMX7 OWT1:OWT7 PGP1:PGP7 PQL1:PQL7 QAH1:QAH7 QKD1:QKD7 QTZ1:QTZ7 RDV1:RDV7 RNR1:RNR7 RXN1:RXN7 SHJ1:SHJ7 SRF1:SRF7 TBB1:TBB7 TKX1:TKX7 TUT1:TUT7 UEP1:UEP7 UOL1:UOL7 UYH1:UYH7 VID1:VID7 VRZ1:VRZ7 WBV1:WBV7 WLR1:WLR7 F1:F1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F$1:F$1048576 JB1:JB7 SX1:SX7 ACT1:ACT7 AMP1:AMP7 AWL1:AWL7 BGH1:BGH7 BQD1:BQD7 BZZ1:BZZ7 CJV1:CJV7 CTR1:CTR7 DDN1:DDN7 DNJ1:DNJ7 DXF1:DXF7 EHB1:EHB7 EQX1:EQX7 FAT1:FAT7 FKP1:FKP7 FUL1:FUL7 GEH1:GEH7 GOD1:GOD7 GXZ1:GXZ7 HHV1:HHV7 HRR1:HRR7 IBN1:IBN7 ILJ1:ILJ7 IVF1:IVF7 JFB1:JFB7 JOX1:JOX7 JYT1:JYT7 KIP1:KIP7 KSL1:KSL7 LCH1:LCH7 LMD1:LMD7 LVZ1:LVZ7 MFV1:MFV7 MPR1:MPR7 MZN1:MZN7 NJJ1:NJJ7 NTF1:NTF7 ODB1:ODB7 OMX1:OMX7 OWT1:OWT7 PGP1:PGP7 PQL1:PQL7 QAH1:QAH7 QKD1:QKD7 QTZ1:QTZ7 RDV1:RDV7 RNR1:RNR7 RXN1:RXN7 SHJ1:SHJ7 SRF1:SRF7 TBB1:TBB7 TKX1:TKX7 TUT1:TUT7 UEP1:UEP7 UOL1:UOL7 UYH1:UYH7 VID1:VID7 VRZ1:VRZ7 WBV1:WBV7 WLR1:WLR7 WVN1:WVN7">
       <formula1>"指定价格,限价指令,市价指令"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrExchangeImport.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrExchangeImport.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>序号</t>
   </si>
@@ -53,6 +53,9 @@
   </si>
   <si>
     <t>结束日期</t>
+  </si>
+  <si>
+    <t>投资目的</t>
   </si>
 </sst>
 </file>
@@ -60,16 +63,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="8">
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="0.000_ "/>
+    <numFmt numFmtId="176" formatCode="0.000_ "/>
+    <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="178" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="179" formatCode="#,##0.00_);[Red]\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -104,26 +107,88 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -137,60 +202,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
@@ -199,54 +210,39 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -261,187 +257,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,11 +466,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -498,7 +500,25 @@
       <right/>
       <top/>
       <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -518,30 +538,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -555,148 +551,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="26" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -707,18 +703,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -728,7 +724,7 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1088,8 +1084,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
+  <dimension ref="A1:O11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="15.5" customWidth="1"/>
     <col min="3" max="3" width="12.375" customWidth="1"/>
@@ -1097,9 +1093,10 @@
     <col min="11" max="11" width="16.75" customWidth="1"/>
     <col min="12" max="12" width="11.625" customWidth="1"/>
     <col min="13" max="13" width="12.25" customWidth="1"/>
+    <col min="14" max="14" width="15.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:13">
+    <row r="1" s="1" customFormat="1" spans="1:14">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1139,8 +1136,11 @@
       <c r="M1" s="10" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:13">
+    <row r="2" s="2" customFormat="1" spans="1:14">
       <c r="A2" s="5"/>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -1154,8 +1154,9 @@
       <c r="K2" s="13"/>
       <c r="L2" s="14"/>
       <c r="M2" s="14"/>
+      <c r="N2"/>
     </row>
-    <row r="3" s="2" customFormat="1" spans="1:13">
+    <row r="3" s="2" customFormat="1" spans="1:14">
       <c r="A3" s="5"/>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -1169,8 +1170,9 @@
       <c r="K3" s="13"/>
       <c r="L3" s="14"/>
       <c r="M3" s="14"/>
+      <c r="N3"/>
     </row>
-    <row r="4" s="2" customFormat="1" spans="1:13">
+    <row r="4" s="2" customFormat="1" spans="1:14">
       <c r="A4" s="5"/>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -1184,8 +1186,9 @@
       <c r="K4" s="13"/>
       <c r="L4" s="14"/>
       <c r="M4" s="14"/>
+      <c r="N4"/>
     </row>
-    <row r="5" s="2" customFormat="1" spans="1:13">
+    <row r="5" s="2" customFormat="1" spans="1:14">
       <c r="A5" s="5"/>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -1199,8 +1202,9 @@
       <c r="K5" s="13"/>
       <c r="L5" s="14"/>
       <c r="M5" s="14"/>
+      <c r="N5"/>
     </row>
-    <row r="6" s="2" customFormat="1" spans="1:13">
+    <row r="6" s="2" customFormat="1" spans="1:14">
       <c r="A6" s="5"/>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -1214,8 +1218,9 @@
       <c r="K6" s="13"/>
       <c r="L6" s="14"/>
       <c r="M6" s="14"/>
+      <c r="N6"/>
     </row>
-    <row r="7" s="2" customFormat="1" spans="1:13">
+    <row r="7" s="2" customFormat="1" spans="1:14">
       <c r="A7" s="5"/>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
@@ -1229,17 +1234,30 @@
       <c r="K7" s="13"/>
       <c r="L7" s="14"/>
       <c r="M7" s="14"/>
+      <c r="N7"/>
+    </row>
+    <row r="9" spans="15:15">
+      <c r="O9" s="2"/>
+    </row>
+    <row r="10" spans="15:15">
+      <c r="O10" s="2"/>
+    </row>
+    <row r="11" spans="15:15">
+      <c r="O11" s="2"/>
     </row>
   </sheetData>
-  <dataValidations count="3">
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="JA7 SW7 ACS7 AMO7 AWK7 BGG7 BQC7 BZY7 CJU7 CTQ7 DDM7 DNI7 DXE7 EHA7 EQW7 FAS7 FKO7 FUK7 GEG7 GOC7 GXY7 HHU7 HRQ7 IBM7 ILI7 IVE7 JFA7 JOW7 JYS7 KIO7 KSK7 LCG7 LMC7 LVY7 MFU7 MPQ7 MZM7 NJI7 NTE7 ODA7 OMW7 OWS7 PGO7 PQK7 QAG7 QKC7 QTY7 RDU7 RNQ7 RXM7 SHI7 SRE7 TBA7 TKW7 TUS7 UEO7 UOK7 UYG7 VIC7 VRY7 WBU7 WLQ7 WVM7 JA1:JA5 SW1:SW5 ACS1:ACS5 AMO1:AMO5 AWK1:AWK5 BGG1:BGG5 BQC1:BQC5 BZY1:BZY5 CJU1:CJU5 CTQ1:CTQ5 DDM1:DDM5 DNI1:DNI5 DXE1:DXE5 EHA1:EHA5 EQW1:EQW5 FAS1:FAS5 FKO1:FKO5 FUK1:FUK5 GEG1:GEG5 GOC1:GOC5 GXY1:GXY5 HHU1:HHU5 HRQ1:HRQ5 IBM1:IBM5 ILI1:ILI5 IVE1:IVE5 JFA1:JFA5 JOW1:JOW5 JYS1:JYS5 KIO1:KIO5 KSK1:KSK5 LCG1:LCG5 LMC1:LMC5 LVY1:LVY5 MFU1:MFU5 MPQ1:MPQ5 MZM1:MZM5 NJI1:NJI5 NTE1:NTE5 ODA1:ODA5 OMW1:OMW5 OWS1:OWS5 PGO1:PGO5 PQK1:PQK5 QAG1:QAG5 QKC1:QKC5 QTY1:QTY5 RDU1:RDU5 RNQ1:RNQ5 RXM1:RXM5 SHI1:SHI5 SRE1:SRE5 TBA1:TBA5 TKW1:TKW5 TUS1:TUS5 UEO1:UEO5 UOK1:UOK5 UYG1:UYG5 VIC1:VIC5 VRY1:VRY5 WBU1:WBU5 WLQ1:WLQ5 WVM1:WVM5">
+      <formula1>"买入,卖出,申购,配股,配债,行权-回售,债转股,质押入库,质押出库,正回购,逆回购"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="JA6 SW6 ACS6 AMO6 AWK6 BGG6 BQC6 BZY6 CJU6 CTQ6 DDM6 DNI6 DXE6 EHA6 EQW6 FAS6 FKO6 FUK6 GEG6 GOC6 GXY6 HHU6 HRQ6 IBM6 ILI6 IVE6 JFA6 JOW6 JYS6 KIO6 KSK6 LCG6 LMC6 LVY6 MFU6 MPQ6 MZM6 NJI6 NTE6 ODA6 OMW6 OWS6 PGO6 PQK6 QAG6 QKC6 QTY6 RDU6 RNQ6 RXM6 SHI6 SRE6 TBA6 TKW6 TUS6 UEO6 UOK6 UYG6 VIC6 VRY6 WBU6 WLQ6 WVM6 E$1:E$1048576">
       <formula1>"买入,卖出,申购,配股,配债,行权-回售,债转股,质押券入库,质押券出库,正回购,逆回购"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="JA7 SW7 ACS7 AMO7 AWK7 BGG7 BQC7 BZY7 CJU7 CTQ7 DDM7 DNI7 DXE7 EHA7 EQW7 FAS7 FKO7 FUK7 GEG7 GOC7 GXY7 HHU7 HRQ7 IBM7 ILI7 IVE7 JFA7 JOW7 JYS7 KIO7 KSK7 LCG7 LMC7 LVY7 MFU7 MPQ7 MZM7 NJI7 NTE7 ODA7 OMW7 OWS7 PGO7 PQK7 QAG7 QKC7 QTY7 RDU7 RNQ7 RXM7 SHI7 SRE7 TBA7 TKW7 TUS7 UEO7 UOK7 UYG7 VIC7 VRY7 WBU7 WLQ7 WVM7 JA1:JA5 SW1:SW5 ACS1:ACS5 AMO1:AMO5 AWK1:AWK5 BGG1:BGG5 BQC1:BQC5 BZY1:BZY5 CJU1:CJU5 CTQ1:CTQ5 DDM1:DDM5 DNI1:DNI5 DXE1:DXE5 EHA1:EHA5 EQW1:EQW5 FAS1:FAS5 FKO1:FKO5 FUK1:FUK5 GEG1:GEG5 GOC1:GOC5 GXY1:GXY5 HHU1:HHU5 HRQ1:HRQ5 IBM1:IBM5 ILI1:ILI5 IVE1:IVE5 JFA1:JFA5 JOW1:JOW5 JYS1:JYS5 KIO1:KIO5 KSK1:KSK5 LCG1:LCG5 LMC1:LMC5 LVY1:LVY5 MFU1:MFU5 MPQ1:MPQ5 MZM1:MZM5 NJI1:NJI5 NTE1:NTE5 ODA1:ODA5 OMW1:OMW5 OWS1:OWS5 PGO1:PGO5 PQK1:PQK5 QAG1:QAG5 QKC1:QKC5 QTY1:QTY5 RDU1:RDU5 RNQ1:RNQ5 RXM1:RXM5 SHI1:SHI5 SRE1:SRE5 TBA1:TBA5 TKW1:TKW5 TUS1:TUS5 UEO1:UEO5 UOK1:UOK5 UYG1:UYG5 VIC1:VIC5 VRY1:VRY5 WBU1:WBU5 WLQ1:WLQ5 WVM1:WVM5">
-      <formula1>"买入,卖出,申购,配股,配债,行权-回售,债转股,质押入库,质押出库,正回购,逆回购"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F$1:F$1048576 JB1:JB7 SX1:SX7 ACT1:ACT7 AMP1:AMP7 AWL1:AWL7 BGH1:BGH7 BQD1:BQD7 BZZ1:BZZ7 CJV1:CJV7 CTR1:CTR7 DDN1:DDN7 DNJ1:DNJ7 DXF1:DXF7 EHB1:EHB7 EQX1:EQX7 FAT1:FAT7 FKP1:FKP7 FUL1:FUL7 GEH1:GEH7 GOD1:GOD7 GXZ1:GXZ7 HHV1:HHV7 HRR1:HRR7 IBN1:IBN7 ILJ1:ILJ7 IVF1:IVF7 JFB1:JFB7 JOX1:JOX7 JYT1:JYT7 KIP1:KIP7 KSL1:KSL7 LCH1:LCH7 LMD1:LMD7 LVZ1:LVZ7 MFV1:MFV7 MPR1:MPR7 MZN1:MZN7 NJJ1:NJJ7 NTF1:NTF7 ODB1:ODB7 OMX1:OMX7 OWT1:OWT7 PGP1:PGP7 PQL1:PQL7 QAH1:QAH7 QKD1:QKD7 QTZ1:QTZ7 RDV1:RDV7 RNR1:RNR7 RXN1:RXN7 SHJ1:SHJ7 SRF1:SRF7 TBB1:TBB7 TKX1:TKX7 TUT1:TUT7 UEP1:UEP7 UOL1:UOL7 UYH1:UYH7 VID1:VID7 VRZ1:VRZ7 WBV1:WBV7 WLR1:WLR7 WVN1:WVN7">
       <formula1>"指定价格,限价指令,市价指令"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N113">
+      <formula1>"以收取该金融资产合同现金流量为目的,以收取该合同现金流量及出售金融资产为目的,以出售该金融资产为目的"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrExchangeImport.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrExchangeImport.xlsx
@@ -63,12 +63,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="8">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0.000_ "/>
-    <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="177" formatCode="0.000_ "/>
     <numFmt numFmtId="178" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="179" formatCode="#,##0.00_);[Red]\(#,##0.00\)"/>
   </numFmts>
@@ -111,10 +111,78 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -126,69 +194,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -210,6 +225,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
@@ -217,32 +241,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -257,25 +257,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -287,7 +377,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -299,145 +419,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -451,17 +451,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -477,6 +473,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -499,6 +510,15 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color theme="4"/>
       </bottom>
@@ -510,15 +530,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -537,27 +548,16 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -569,130 +569,130 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -703,18 +703,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -724,7 +724,7 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1136,7 +1136,7 @@
       <c r="M1" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="10" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1247,14 +1247,14 @@
     </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="JA7 SW7 ACS7 AMO7 AWK7 BGG7 BQC7 BZY7 CJU7 CTQ7 DDM7 DNI7 DXE7 EHA7 EQW7 FAS7 FKO7 FUK7 GEG7 GOC7 GXY7 HHU7 HRQ7 IBM7 ILI7 IVE7 JFA7 JOW7 JYS7 KIO7 KSK7 LCG7 LMC7 LVY7 MFU7 MPQ7 MZM7 NJI7 NTE7 ODA7 OMW7 OWS7 PGO7 PQK7 QAG7 QKC7 QTY7 RDU7 RNQ7 RXM7 SHI7 SRE7 TBA7 TKW7 TUS7 UEO7 UOK7 UYG7 VIC7 VRY7 WBU7 WLQ7 WVM7 JA1:JA5 SW1:SW5 ACS1:ACS5 AMO1:AMO5 AWK1:AWK5 BGG1:BGG5 BQC1:BQC5 BZY1:BZY5 CJU1:CJU5 CTQ1:CTQ5 DDM1:DDM5 DNI1:DNI5 DXE1:DXE5 EHA1:EHA5 EQW1:EQW5 FAS1:FAS5 FKO1:FKO5 FUK1:FUK5 GEG1:GEG5 GOC1:GOC5 GXY1:GXY5 HHU1:HHU5 HRQ1:HRQ5 IBM1:IBM5 ILI1:ILI5 IVE1:IVE5 JFA1:JFA5 JOW1:JOW5 JYS1:JYS5 KIO1:KIO5 KSK1:KSK5 LCG1:LCG5 LMC1:LMC5 LVY1:LVY5 MFU1:MFU5 MPQ1:MPQ5 MZM1:MZM5 NJI1:NJI5 NTE1:NTE5 ODA1:ODA5 OMW1:OMW5 OWS1:OWS5 PGO1:PGO5 PQK1:PQK5 QAG1:QAG5 QKC1:QKC5 QTY1:QTY5 RDU1:RDU5 RNQ1:RNQ5 RXM1:RXM5 SHI1:SHI5 SRE1:SRE5 TBA1:TBA5 TKW1:TKW5 TUS1:TUS5 UEO1:UEO5 UOK1:UOK5 UYG1:UYG5 VIC1:VIC5 VRY1:VRY5 WBU1:WBU5 WLQ1:WLQ5 WVM1:WVM5">
-      <formula1>"买入,卖出,申购,配股,配债,行权-回售,债转股,质押入库,质押出库,正回购,逆回购"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="JA6 SW6 ACS6 AMO6 AWK6 BGG6 BQC6 BZY6 CJU6 CTQ6 DDM6 DNI6 DXE6 EHA6 EQW6 FAS6 FKO6 FUK6 GEG6 GOC6 GXY6 HHU6 HRQ6 IBM6 ILI6 IVE6 JFA6 JOW6 JYS6 KIO6 KSK6 LCG6 LMC6 LVY6 MFU6 MPQ6 MZM6 NJI6 NTE6 ODA6 OMW6 OWS6 PGO6 PQK6 QAG6 QKC6 QTY6 RDU6 RNQ6 RXM6 SHI6 SRE6 TBA6 TKW6 TUS6 UEO6 UOK6 UYG6 VIC6 VRY6 WBU6 WLQ6 WVM6 E$1:E$1048576">
       <formula1>"买入,卖出,申购,配股,配债,行权-回售,债转股,质押券入库,质押券出库,正回购,逆回购"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F$1:F$1048576 JB1:JB7 SX1:SX7 ACT1:ACT7 AMP1:AMP7 AWL1:AWL7 BGH1:BGH7 BQD1:BQD7 BZZ1:BZZ7 CJV1:CJV7 CTR1:CTR7 DDN1:DDN7 DNJ1:DNJ7 DXF1:DXF7 EHB1:EHB7 EQX1:EQX7 FAT1:FAT7 FKP1:FKP7 FUL1:FUL7 GEH1:GEH7 GOD1:GOD7 GXZ1:GXZ7 HHV1:HHV7 HRR1:HRR7 IBN1:IBN7 ILJ1:ILJ7 IVF1:IVF7 JFB1:JFB7 JOX1:JOX7 JYT1:JYT7 KIP1:KIP7 KSL1:KSL7 LCH1:LCH7 LMD1:LMD7 LVZ1:LVZ7 MFV1:MFV7 MPR1:MPR7 MZN1:MZN7 NJJ1:NJJ7 NTF1:NTF7 ODB1:ODB7 OMX1:OMX7 OWT1:OWT7 PGP1:PGP7 PQL1:PQL7 QAH1:QAH7 QKD1:QKD7 QTZ1:QTZ7 RDV1:RDV7 RNR1:RNR7 RXN1:RXN7 SHJ1:SHJ7 SRF1:SRF7 TBB1:TBB7 TKX1:TKX7 TUT1:TUT7 UEP1:UEP7 UOL1:UOL7 UYH1:UYH7 VID1:VID7 VRZ1:VRZ7 WBV1:WBV7 WLR1:WLR7 WVN1:WVN7">
       <formula1>"指定价格,限价指令,市价指令"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="JA7 SW7 ACS7 AMO7 AWK7 BGG7 BQC7 BZY7 CJU7 CTQ7 DDM7 DNI7 DXE7 EHA7 EQW7 FAS7 FKO7 FUK7 GEG7 GOC7 GXY7 HHU7 HRQ7 IBM7 ILI7 IVE7 JFA7 JOW7 JYS7 KIO7 KSK7 LCG7 LMC7 LVY7 MFU7 MPQ7 MZM7 NJI7 NTE7 ODA7 OMW7 OWS7 PGO7 PQK7 QAG7 QKC7 QTY7 RDU7 RNQ7 RXM7 SHI7 SRE7 TBA7 TKW7 TUS7 UEO7 UOK7 UYG7 VIC7 VRY7 WBU7 WLQ7 WVM7 JA1:JA5 SW1:SW5 ACS1:ACS5 AMO1:AMO5 AWK1:AWK5 BGG1:BGG5 BQC1:BQC5 BZY1:BZY5 CJU1:CJU5 CTQ1:CTQ5 DDM1:DDM5 DNI1:DNI5 DXE1:DXE5 EHA1:EHA5 EQW1:EQW5 FAS1:FAS5 FKO1:FKO5 FUK1:FUK5 GEG1:GEG5 GOC1:GOC5 GXY1:GXY5 HHU1:HHU5 HRQ1:HRQ5 IBM1:IBM5 ILI1:ILI5 IVE1:IVE5 JFA1:JFA5 JOW1:JOW5 JYS1:JYS5 KIO1:KIO5 KSK1:KSK5 LCG1:LCG5 LMC1:LMC5 LVY1:LVY5 MFU1:MFU5 MPQ1:MPQ5 MZM1:MZM5 NJI1:NJI5 NTE1:NTE5 ODA1:ODA5 OMW1:OMW5 OWS1:OWS5 PGO1:PGO5 PQK1:PQK5 QAG1:QAG5 QKC1:QKC5 QTY1:QTY5 RDU1:RDU5 RNQ1:RNQ5 RXM1:RXM5 SHI1:SHI5 SRE1:SRE5 TBA1:TBA5 TKW1:TKW5 TUS1:TUS5 UEO1:UEO5 UOK1:UOK5 UYG1:UYG5 VIC1:VIC5 VRY1:VRY5 WBU1:WBU5 WLQ1:WLQ5 WVM1:WVM5">
+      <formula1>"买入,卖出,申购,配股,配债,行权-回售,债转股,质押入库,质押出库,正回购,逆回购"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N113">
       <formula1>"以收取该金融资产合同现金流量为目的,以收取该合同现金流量及出售金融资产为目的,以出售该金融资产为目的"</formula1>

--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrExchangeImport.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrExchangeImport.xlsx
@@ -63,12 +63,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="8">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0.000_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="177" formatCode="0.000_ "/>
+    <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="178" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="179" formatCode="#,##0.00_);[Red]\(#,##0.00\)"/>
   </numFmts>
@@ -105,84 +105,61 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -202,13 +179,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -235,7 +205,37 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -257,187 +257,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -448,32 +448,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -510,15 +484,6 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="medium">
         <color theme="4"/>
       </bottom>
@@ -548,16 +513,51 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -566,155 +566,155 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -724,7 +724,7 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -736,6 +736,7 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1084,7 +1085,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O108"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="15.5" customWidth="1"/>
@@ -1154,7 +1155,7 @@
       <c r="K2" s="13"/>
       <c r="L2" s="14"/>
       <c r="M2" s="14"/>
-      <c r="N2"/>
+      <c r="N2" s="15"/>
     </row>
     <row r="3" s="2" customFormat="1" spans="1:14">
       <c r="A3" s="5"/>
@@ -1170,7 +1171,7 @@
       <c r="K3" s="13"/>
       <c r="L3" s="14"/>
       <c r="M3" s="14"/>
-      <c r="N3"/>
+      <c r="N3" s="15"/>
     </row>
     <row r="4" s="2" customFormat="1" spans="1:14">
       <c r="A4" s="5"/>
@@ -1186,7 +1187,7 @@
       <c r="K4" s="13"/>
       <c r="L4" s="14"/>
       <c r="M4" s="14"/>
-      <c r="N4"/>
+      <c r="N4" s="15"/>
     </row>
     <row r="5" s="2" customFormat="1" spans="1:14">
       <c r="A5" s="5"/>
@@ -1202,7 +1203,7 @@
       <c r="K5" s="13"/>
       <c r="L5" s="14"/>
       <c r="M5" s="14"/>
-      <c r="N5"/>
+      <c r="N5" s="15"/>
     </row>
     <row r="6" s="2" customFormat="1" spans="1:14">
       <c r="A6" s="5"/>
@@ -1218,7 +1219,7 @@
       <c r="K6" s="13"/>
       <c r="L6" s="14"/>
       <c r="M6" s="14"/>
-      <c r="N6"/>
+      <c r="N6" s="15"/>
     </row>
     <row r="7" s="2" customFormat="1" spans="1:14">
       <c r="A7" s="5"/>
@@ -1234,30 +1235,327 @@
       <c r="K7" s="13"/>
       <c r="L7" s="14"/>
       <c r="M7" s="14"/>
-      <c r="N7"/>
-    </row>
-    <row r="9" spans="15:15">
+      <c r="N7" s="15"/>
+    </row>
+    <row r="8" spans="14:14">
+      <c r="N8" s="15"/>
+    </row>
+    <row r="9" spans="14:15">
+      <c r="N9" s="15"/>
       <c r="O9" s="2"/>
     </row>
-    <row r="10" spans="15:15">
+    <row r="10" spans="14:15">
+      <c r="N10" s="15"/>
       <c r="O10" s="2"/>
     </row>
-    <row r="11" spans="15:15">
+    <row r="11" spans="14:15">
+      <c r="N11" s="15"/>
       <c r="O11" s="2"/>
+    </row>
+    <row r="12" spans="14:14">
+      <c r="N12" s="15"/>
+    </row>
+    <row r="13" spans="14:14">
+      <c r="N13" s="15"/>
+    </row>
+    <row r="14" spans="14:14">
+      <c r="N14" s="15"/>
+    </row>
+    <row r="15" spans="14:14">
+      <c r="N15" s="15"/>
+    </row>
+    <row r="16" spans="14:14">
+      <c r="N16" s="15"/>
+    </row>
+    <row r="17" spans="14:14">
+      <c r="N17" s="15"/>
+    </row>
+    <row r="18" spans="14:14">
+      <c r="N18" s="15"/>
+    </row>
+    <row r="19" spans="14:14">
+      <c r="N19" s="15"/>
+    </row>
+    <row r="20" spans="14:14">
+      <c r="N20" s="15"/>
+    </row>
+    <row r="21" spans="14:14">
+      <c r="N21" s="15"/>
+    </row>
+    <row r="22" spans="14:14">
+      <c r="N22" s="15"/>
+    </row>
+    <row r="23" spans="14:14">
+      <c r="N23" s="15"/>
+    </row>
+    <row r="24" spans="14:14">
+      <c r="N24" s="15"/>
+    </row>
+    <row r="25" spans="14:14">
+      <c r="N25" s="15"/>
+    </row>
+    <row r="26" spans="14:14">
+      <c r="N26" s="15"/>
+    </row>
+    <row r="27" spans="14:14">
+      <c r="N27" s="15"/>
+    </row>
+    <row r="28" spans="14:14">
+      <c r="N28" s="15"/>
+    </row>
+    <row r="29" spans="14:14">
+      <c r="N29" s="15"/>
+    </row>
+    <row r="30" spans="14:14">
+      <c r="N30" s="15"/>
+    </row>
+    <row r="31" spans="14:14">
+      <c r="N31" s="15"/>
+    </row>
+    <row r="32" spans="14:14">
+      <c r="N32" s="15"/>
+    </row>
+    <row r="33" spans="14:14">
+      <c r="N33" s="15"/>
+    </row>
+    <row r="34" spans="14:14">
+      <c r="N34" s="15"/>
+    </row>
+    <row r="35" spans="14:14">
+      <c r="N35" s="15"/>
+    </row>
+    <row r="36" spans="14:14">
+      <c r="N36" s="15"/>
+    </row>
+    <row r="37" spans="14:14">
+      <c r="N37" s="15"/>
+    </row>
+    <row r="38" spans="14:14">
+      <c r="N38" s="15"/>
+    </row>
+    <row r="39" spans="14:14">
+      <c r="N39" s="15"/>
+    </row>
+    <row r="40" spans="14:14">
+      <c r="N40" s="15"/>
+    </row>
+    <row r="41" spans="14:14">
+      <c r="N41" s="15"/>
+    </row>
+    <row r="42" spans="14:14">
+      <c r="N42" s="15"/>
+    </row>
+    <row r="43" spans="14:14">
+      <c r="N43" s="15"/>
+    </row>
+    <row r="44" spans="14:14">
+      <c r="N44" s="15"/>
+    </row>
+    <row r="45" spans="14:14">
+      <c r="N45" s="15"/>
+    </row>
+    <row r="46" spans="14:14">
+      <c r="N46" s="15"/>
+    </row>
+    <row r="47" spans="14:14">
+      <c r="N47" s="15"/>
+    </row>
+    <row r="48" spans="14:14">
+      <c r="N48" s="15"/>
+    </row>
+    <row r="49" spans="14:14">
+      <c r="N49" s="15"/>
+    </row>
+    <row r="50" spans="14:14">
+      <c r="N50" s="15"/>
+    </row>
+    <row r="51" spans="14:14">
+      <c r="N51" s="15"/>
+    </row>
+    <row r="52" spans="14:14">
+      <c r="N52" s="15"/>
+    </row>
+    <row r="53" spans="14:14">
+      <c r="N53" s="15"/>
+    </row>
+    <row r="54" spans="14:14">
+      <c r="N54" s="15"/>
+    </row>
+    <row r="55" spans="14:14">
+      <c r="N55" s="15"/>
+    </row>
+    <row r="56" spans="14:14">
+      <c r="N56" s="15"/>
+    </row>
+    <row r="57" spans="14:14">
+      <c r="N57" s="15"/>
+    </row>
+    <row r="58" spans="14:14">
+      <c r="N58" s="15"/>
+    </row>
+    <row r="59" spans="14:14">
+      <c r="N59" s="15"/>
+    </row>
+    <row r="60" spans="14:14">
+      <c r="N60" s="15"/>
+    </row>
+    <row r="61" spans="14:14">
+      <c r="N61" s="15"/>
+    </row>
+    <row r="62" spans="14:14">
+      <c r="N62" s="15"/>
+    </row>
+    <row r="63" spans="14:14">
+      <c r="N63" s="15"/>
+    </row>
+    <row r="64" spans="14:14">
+      <c r="N64" s="15"/>
+    </row>
+    <row r="65" spans="14:14">
+      <c r="N65" s="15"/>
+    </row>
+    <row r="66" spans="14:14">
+      <c r="N66" s="15"/>
+    </row>
+    <row r="67" spans="14:14">
+      <c r="N67" s="15"/>
+    </row>
+    <row r="68" spans="14:14">
+      <c r="N68" s="15"/>
+    </row>
+    <row r="69" spans="14:14">
+      <c r="N69" s="15"/>
+    </row>
+    <row r="70" spans="14:14">
+      <c r="N70" s="15"/>
+    </row>
+    <row r="71" spans="14:14">
+      <c r="N71" s="15"/>
+    </row>
+    <row r="72" spans="14:14">
+      <c r="N72" s="15"/>
+    </row>
+    <row r="73" spans="14:14">
+      <c r="N73" s="15"/>
+    </row>
+    <row r="74" spans="14:14">
+      <c r="N74" s="15"/>
+    </row>
+    <row r="75" spans="14:14">
+      <c r="N75" s="15"/>
+    </row>
+    <row r="76" spans="14:14">
+      <c r="N76" s="15"/>
+    </row>
+    <row r="77" spans="14:14">
+      <c r="N77" s="15"/>
+    </row>
+    <row r="78" spans="14:14">
+      <c r="N78" s="15"/>
+    </row>
+    <row r="79" spans="14:14">
+      <c r="N79" s="15"/>
+    </row>
+    <row r="80" spans="14:14">
+      <c r="N80" s="15"/>
+    </row>
+    <row r="81" spans="14:14">
+      <c r="N81" s="15"/>
+    </row>
+    <row r="82" spans="14:14">
+      <c r="N82" s="15"/>
+    </row>
+    <row r="83" spans="14:14">
+      <c r="N83" s="15"/>
+    </row>
+    <row r="84" spans="14:14">
+      <c r="N84" s="15"/>
+    </row>
+    <row r="85" spans="14:14">
+      <c r="N85" s="15"/>
+    </row>
+    <row r="86" spans="14:14">
+      <c r="N86" s="15"/>
+    </row>
+    <row r="87" spans="14:14">
+      <c r="N87" s="15"/>
+    </row>
+    <row r="88" spans="14:14">
+      <c r="N88" s="15"/>
+    </row>
+    <row r="89" spans="14:14">
+      <c r="N89" s="15"/>
+    </row>
+    <row r="90" spans="14:14">
+      <c r="N90" s="15"/>
+    </row>
+    <row r="91" spans="14:14">
+      <c r="N91" s="15"/>
+    </row>
+    <row r="92" spans="14:14">
+      <c r="N92" s="15"/>
+    </row>
+    <row r="93" spans="14:14">
+      <c r="N93" s="15"/>
+    </row>
+    <row r="94" spans="14:14">
+      <c r="N94" s="15"/>
+    </row>
+    <row r="95" spans="14:14">
+      <c r="N95" s="15"/>
+    </row>
+    <row r="96" spans="14:14">
+      <c r="N96" s="15"/>
+    </row>
+    <row r="97" spans="14:14">
+      <c r="N97" s="15"/>
+    </row>
+    <row r="98" spans="14:14">
+      <c r="N98" s="15"/>
+    </row>
+    <row r="99" spans="14:14">
+      <c r="N99" s="15"/>
+    </row>
+    <row r="100" spans="14:14">
+      <c r="N100" s="15"/>
+    </row>
+    <row r="101" spans="14:14">
+      <c r="N101" s="15"/>
+    </row>
+    <row r="102" spans="14:14">
+      <c r="N102" s="15"/>
+    </row>
+    <row r="103" spans="14:14">
+      <c r="N103" s="15"/>
+    </row>
+    <row r="104" spans="14:14">
+      <c r="N104" s="15"/>
+    </row>
+    <row r="105" spans="14:14">
+      <c r="N105" s="15"/>
+    </row>
+    <row r="106" spans="14:14">
+      <c r="N106" s="15"/>
+    </row>
+    <row r="107" spans="14:14">
+      <c r="N107" s="15"/>
+    </row>
+    <row r="108" spans="14:14">
+      <c r="N108" s="15"/>
     </row>
   </sheetData>
   <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N108 N109:N113">
+      <formula1>"以收取该金融资产合同现金流量为目的,以收取该合同现金流量及出售金融资产为目的,以出售该金融资产为目的"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="JA6 SW6 ACS6 AMO6 AWK6 BGG6 BQC6 BZY6 CJU6 CTQ6 DDM6 DNI6 DXE6 EHA6 EQW6 FAS6 FKO6 FUK6 GEG6 GOC6 GXY6 HHU6 HRQ6 IBM6 ILI6 IVE6 JFA6 JOW6 JYS6 KIO6 KSK6 LCG6 LMC6 LVY6 MFU6 MPQ6 MZM6 NJI6 NTE6 ODA6 OMW6 OWS6 PGO6 PQK6 QAG6 QKC6 QTY6 RDU6 RNQ6 RXM6 SHI6 SRE6 TBA6 TKW6 TUS6 UEO6 UOK6 UYG6 VIC6 VRY6 WBU6 WLQ6 WVM6 E$1:E$1048576">
       <formula1>"买入,卖出,申购,配股,配债,行权-回售,债转股,质押券入库,质押券出库,正回购,逆回购"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F$1:F$1048576 JB1:JB7 SX1:SX7 ACT1:ACT7 AMP1:AMP7 AWL1:AWL7 BGH1:BGH7 BQD1:BQD7 BZZ1:BZZ7 CJV1:CJV7 CTR1:CTR7 DDN1:DDN7 DNJ1:DNJ7 DXF1:DXF7 EHB1:EHB7 EQX1:EQX7 FAT1:FAT7 FKP1:FKP7 FUL1:FUL7 GEH1:GEH7 GOD1:GOD7 GXZ1:GXZ7 HHV1:HHV7 HRR1:HRR7 IBN1:IBN7 ILJ1:ILJ7 IVF1:IVF7 JFB1:JFB7 JOX1:JOX7 JYT1:JYT7 KIP1:KIP7 KSL1:KSL7 LCH1:LCH7 LMD1:LMD7 LVZ1:LVZ7 MFV1:MFV7 MPR1:MPR7 MZN1:MZN7 NJJ1:NJJ7 NTF1:NTF7 ODB1:ODB7 OMX1:OMX7 OWT1:OWT7 PGP1:PGP7 PQL1:PQL7 QAH1:QAH7 QKD1:QKD7 QTZ1:QTZ7 RDV1:RDV7 RNR1:RNR7 RXN1:RXN7 SHJ1:SHJ7 SRF1:SRF7 TBB1:TBB7 TKX1:TKX7 TUT1:TUT7 UEP1:UEP7 UOL1:UOL7 UYH1:UYH7 VID1:VID7 VRZ1:VRZ7 WBV1:WBV7 WLR1:WLR7 WVN1:WVN7">
-      <formula1>"指定价格,限价指令,市价指令"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="JA7 SW7 ACS7 AMO7 AWK7 BGG7 BQC7 BZY7 CJU7 CTQ7 DDM7 DNI7 DXE7 EHA7 EQW7 FAS7 FKO7 FUK7 GEG7 GOC7 GXY7 HHU7 HRQ7 IBM7 ILI7 IVE7 JFA7 JOW7 JYS7 KIO7 KSK7 LCG7 LMC7 LVY7 MFU7 MPQ7 MZM7 NJI7 NTE7 ODA7 OMW7 OWS7 PGO7 PQK7 QAG7 QKC7 QTY7 RDU7 RNQ7 RXM7 SHI7 SRE7 TBA7 TKW7 TUS7 UEO7 UOK7 UYG7 VIC7 VRY7 WBU7 WLQ7 WVM7 JA1:JA5 SW1:SW5 ACS1:ACS5 AMO1:AMO5 AWK1:AWK5 BGG1:BGG5 BQC1:BQC5 BZY1:BZY5 CJU1:CJU5 CTQ1:CTQ5 DDM1:DDM5 DNI1:DNI5 DXE1:DXE5 EHA1:EHA5 EQW1:EQW5 FAS1:FAS5 FKO1:FKO5 FUK1:FUK5 GEG1:GEG5 GOC1:GOC5 GXY1:GXY5 HHU1:HHU5 HRQ1:HRQ5 IBM1:IBM5 ILI1:ILI5 IVE1:IVE5 JFA1:JFA5 JOW1:JOW5 JYS1:JYS5 KIO1:KIO5 KSK1:KSK5 LCG1:LCG5 LMC1:LMC5 LVY1:LVY5 MFU1:MFU5 MPQ1:MPQ5 MZM1:MZM5 NJI1:NJI5 NTE1:NTE5 ODA1:ODA5 OMW1:OMW5 OWS1:OWS5 PGO1:PGO5 PQK1:PQK5 QAG1:QAG5 QKC1:QKC5 QTY1:QTY5 RDU1:RDU5 RNQ1:RNQ5 RXM1:RXM5 SHI1:SHI5 SRE1:SRE5 TBA1:TBA5 TKW1:TKW5 TUS1:TUS5 UEO1:UEO5 UOK1:UOK5 UYG1:UYG5 VIC1:VIC5 VRY1:VRY5 WBU1:WBU5 WLQ1:WLQ5 WVM1:WVM5">
       <formula1>"买入,卖出,申购,配股,配债,行权-回售,债转股,质押入库,质押出库,正回购,逆回购"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N113">
-      <formula1>"以收取该金融资产合同现金流量为目的,以收取该合同现金流量及出售金融资产为目的,以出售该金融资产为目的"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F$1:F$1048576 JB1:JB7 SX1:SX7 ACT1:ACT7 AMP1:AMP7 AWL1:AWL7 BGH1:BGH7 BQD1:BQD7 BZZ1:BZZ7 CJV1:CJV7 CTR1:CTR7 DDN1:DDN7 DNJ1:DNJ7 DXF1:DXF7 EHB1:EHB7 EQX1:EQX7 FAT1:FAT7 FKP1:FKP7 FUL1:FUL7 GEH1:GEH7 GOD1:GOD7 GXZ1:GXZ7 HHV1:HHV7 HRR1:HRR7 IBN1:IBN7 ILJ1:ILJ7 IVF1:IVF7 JFB1:JFB7 JOX1:JOX7 JYT1:JYT7 KIP1:KIP7 KSL1:KSL7 LCH1:LCH7 LMD1:LMD7 LVZ1:LVZ7 MFV1:MFV7 MPR1:MPR7 MZN1:MZN7 NJJ1:NJJ7 NTF1:NTF7 ODB1:ODB7 OMX1:OMX7 OWT1:OWT7 PGP1:PGP7 PQL1:PQL7 QAH1:QAH7 QKD1:QKD7 QTZ1:QTZ7 RDV1:RDV7 RNR1:RNR7 RXN1:RXN7 SHJ1:SHJ7 SRF1:SRF7 TBB1:TBB7 TKX1:TKX7 TUT1:TUT7 UEP1:UEP7 UOL1:UOL7 UYH1:UYH7 VID1:VID7 VRZ1:VRZ7 WBV1:WBV7 WLR1:WLR7 WVN1:WVN7">
+      <formula1>"指定价格,限价指令,市价指令"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
